--- a/planering/biologi-omrade4/biologi-4-kahoot.xlsx
+++ b/planering/biologi-omrade4/biologi-4-kahoot.xlsx
@@ -1932,17 +1932,17 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
+          <t>Båda</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Abiotisk</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
           <t>Biotisk</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Abiotisk</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Båda</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Biotop</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
           <t>Nisch</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Biotop</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Population</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
+          <t>populationen</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
           <t>näringsväven</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>biotopen</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>populationen</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2160,22 +2160,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
+          <t>Uppåt</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Mot den som äter</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
           <t>Mot den som blir äten</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Mot den som äter</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Mot solen</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Uppåt</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
+          <t>Toppkonsumenter</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Växtätare</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Nedbrytare, till exempel svampar och bakterier</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
           <t>Producenter</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Växtätare</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Nedbrytare, till exempel svampar och bakterier</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Toppkonsumenter</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2274,17 +2274,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
+          <t>Näringsnisch</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
           <t>Kretslopp</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Biosfär</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Näringsnisch</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
+          <t>Konkurrens</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
           <t>Bärkraft</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Konkurrens</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -2388,22 +2388,22 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
+          <t>Från nedbrytarna</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Från solen</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
           <t>Från växternas rötter</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Från solen</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Från jorden</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Från nedbrytarna</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
+          <t>Biomassa</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
           <t>Glukos</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Biomassa</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
+          <t>Förna</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
           <t>Bärkraft</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Population</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Förna</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Ingen av dem</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
           <t>Båda</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Ingen av dem</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Materia</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Energi</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
+          <t>Cellandning</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Nedbrytning</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
           <t>Förbränning</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Cellandning</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Nedbrytning</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
+          <t>Pollinering</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Osmos</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
           <t>Fotosyntes</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Osmos</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Pollinering</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2844,22 +2844,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
+          <t>biomassa</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>förna</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
           <t>bärkraft</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>förna</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>nisch</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>biomassa</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
